--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97255\Desktop\עבודה\מונדיאל\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723A7299-1722-4B89-973F-D97D9B624783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD63A067-39E3-4C8A-B0F7-B5AB66916DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A019FD43-B7E8-4CA3-B816-C81C6E53015D}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A019FD43-B7E8-4CA3-B816-C81C6E53015D}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -569,13 +569,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3">
         <v>2</v>
@@ -599,15 +599,15 @@
       </c>
       <c r="B4" s="2">
         <f>B3/B2</f>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ref="C4:D4" si="0">C3/C2</f>
-        <v>0</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="3">
         <v>3</v>

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97255\Desktop\עבודה\מונדיאל\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD63A067-39E3-4C8A-B0F7-B5AB66916DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB439DE-44E5-434C-8310-0B7FF73EC6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A019FD43-B7E8-4CA3-B816-C81C6E53015D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A019FD43-B7E8-4CA3-B816-C81C6E53015D}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>צוות אלפא</t>
   </si>
@@ -68,36 +68,6 @@
     <t>כמות לידים</t>
   </si>
   <si>
-    <t>דוד</t>
-  </si>
-  <si>
-    <t>מיכטל</t>
-  </si>
-  <si>
-    <t>אודיה</t>
-  </si>
-  <si>
-    <t>רונית</t>
-  </si>
-  <si>
-    <t>מירב</t>
-  </si>
-  <si>
-    <t>שני</t>
-  </si>
-  <si>
-    <t>הודיה</t>
-  </si>
-  <si>
-    <t>אביגיך</t>
-  </si>
-  <si>
-    <t>מני</t>
-  </si>
-  <si>
-    <t>חילך</t>
-  </si>
-  <si>
     <t>מבזקים</t>
   </si>
   <si>
@@ -111,6 +81,15 @@
   </si>
   <si>
     <t>צוות אלפא עמד ביעד! מתקרב ל120% ביצוע! |</t>
+  </si>
+  <si>
+    <t>אירנה מסוצניק</t>
+  </si>
+  <si>
+    <t>איילה שלי</t>
+  </si>
+  <si>
+    <t>סיון יוסף</t>
   </si>
 </sst>
 </file>
@@ -156,16 +135,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -506,7 +482,9 @@
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -519,20 +497,20 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -540,28 +518,28 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1">
-        <v>20</v>
-      </c>
-      <c r="G2" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="K2" s="4">
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2</v>
+      </c>
+      <c r="K2" s="3">
         <v>0.42986111111111108</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -569,28 +547,28 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3">
         <v>2</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3">
         <v>0.43055555555555558</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -599,108 +577,66 @@
       </c>
       <c r="B4" s="2">
         <f>B3/B2</f>
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ref="C4:D4" si="0">C3/C2</f>
-        <v>1.1499999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G4" s="1">
         <v>3</v>
       </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4">
+      <c r="H4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.43263888888888885</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G5" s="1">
+        <v>4</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G6" s="1">
         <v>5</v>
       </c>
-      <c r="K4" s="4">
-        <v>0.43263888888888885</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G5" s="3">
-        <v>4</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G6" s="3">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G7" s="3">
+      <c r="G7" s="1">
         <v>6</v>
       </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G8" s="3">
+      <c r="G8" s="1">
         <v>7</v>
       </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G9" s="3">
+      <c r="G9" s="1">
         <v>8</v>
       </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G10" s="3">
+      <c r="G10" s="1">
         <v>9</v>
       </c>
-      <c r="H10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G11" s="3">
+      <c r="G11" s="1">
         <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
